--- a/Sup Tables/Table S10 InsDel_N burden by MSI status.xlsx
+++ b/Sup Tables/Table S10 InsDel_N burden by MSI status.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
-    <t xml:space="preserve">Table S10, Signature InsDel_N_alpha and InsDel_N_beta burden by MSI status and in conjunction with InsDel1a/1b/1c mutations. Any: All analyzed tumors of that MSI status, whatever signatures they carry. This row is the reference for the rows below it. Overlapping categories: The four InsDel1-family rows dissect co-occurrence with InsDel_N_beta and are not disjoint. A tumor with InsDel_N_beta, InsDel1a and InsDel1b is counted in both the 'and InsDel1a' and the 'and InsDel1b/1c' rows. Tumors analyzed: 6945 of 6975 (175 MSI-H, 6770 MSS). Source data: liu_et_al_89_assignment.tsv and sample_info.tsv from https://github.com/indelsig/unified_indels_data/. Generated by: build_sup_table_insdel_N/build_sup_table_insdel_N.R.</t>
+    <t xml:space="preserve">Table S10, Signature InsDel_N_alpha and InsDel_N_beta burden by MSI status and in conjunction with InsDel1a/1b/1c mutations. Any: All analyzed tumors of that MSI status, whatever signatures they carry. This row is the reference for the rows below it. Overlapping categories: The four InsDel1-family rows dissect co-occurrence with InsDel_N_beta and are not disjoint. A tumor with InsDel_N_beta, InsDel1a and InsDel1b is counted in both the 'and InsDel1a' and the 'and InsDel1b/1c' rows. Tumors analyzed: 6945 of 6975 (175 MSI-H, 6770 MSS). Source data: liu_et_al_89_assignment.tsv and sample_info.tsv from https://github.com/indelsig/unified_indels_data/. Generated by: build_sup_table_s10/build_sup_table_s10.R.</t>
   </si>
   <si>
     <t xml:space="preserve">MSI status</t>
